--- a/output/yearly_population_iteration_39_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_39_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6500</v>
+        <v>4913</v>
       </c>
       <c r="C2" t="n">
-        <v>10750</v>
+        <v>13494</v>
       </c>
       <c r="D2" t="n">
-        <v>22393</v>
+        <v>30228</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4640</v>
+        <v>3774</v>
       </c>
       <c r="C3" t="n">
-        <v>5923</v>
+        <v>5208</v>
       </c>
       <c r="D3" t="n">
-        <v>14185</v>
+        <v>16914</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3648</v>
+        <v>2807</v>
       </c>
       <c r="C4" t="n">
-        <v>5408</v>
+        <v>5607</v>
       </c>
       <c r="D4" t="n">
-        <v>6730</v>
+        <v>8731</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2270</v>
+        <v>1702</v>
       </c>
       <c r="C5" t="n">
-        <v>3792</v>
+        <v>4798</v>
       </c>
       <c r="D5" t="n">
-        <v>2495</v>
+        <v>3243</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1285</v>
+        <v>972</v>
       </c>
       <c r="C6" t="n">
-        <v>2537</v>
+        <v>3553</v>
       </c>
       <c r="D6" t="n">
-        <v>1061</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>610</v>
+        <v>444</v>
       </c>
       <c r="C7" t="n">
-        <v>1708</v>
+        <v>2234</v>
       </c>
       <c r="D7" t="n">
-        <v>637</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>230</v>
+        <v>165</v>
       </c>
       <c r="C8" t="n">
-        <v>866</v>
+        <v>1059</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>380</v>
+        <v>436</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8750</v>
+        <v>5984</v>
       </c>
       <c r="C2" t="n">
-        <v>9670</v>
+        <v>18066</v>
       </c>
       <c r="D2" t="n">
-        <v>31609</v>
+        <v>28466</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4476</v>
+        <v>3501</v>
       </c>
       <c r="C3" t="n">
-        <v>7143</v>
+        <v>7781</v>
       </c>
       <c r="D3" t="n">
-        <v>14348</v>
+        <v>17508</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3525</v>
+        <v>2768</v>
       </c>
       <c r="C4" t="n">
-        <v>5490</v>
+        <v>5306</v>
       </c>
       <c r="D4" t="n">
-        <v>7742</v>
+        <v>9638</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2522</v>
+        <v>1899</v>
       </c>
       <c r="C5" t="n">
-        <v>4473</v>
+        <v>5009</v>
       </c>
       <c r="D5" t="n">
-        <v>3045</v>
+        <v>3987</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1554</v>
+        <v>1156</v>
       </c>
       <c r="C6" t="n">
-        <v>3053</v>
+        <v>4057</v>
       </c>
       <c r="D6" t="n">
-        <v>1267</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>811</v>
+        <v>589</v>
       </c>
       <c r="C7" t="n">
-        <v>2081</v>
+        <v>2767</v>
       </c>
       <c r="D7" t="n">
-        <v>686</v>
+        <v>742</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>341</v>
+        <v>245</v>
       </c>
       <c r="C8" t="n">
-        <v>1220</v>
+        <v>1531</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>584</v>
+        <v>686</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9342</v>
+        <v>7758</v>
       </c>
       <c r="C2" t="n">
-        <v>14586</v>
+        <v>17823</v>
       </c>
       <c r="D2" t="n">
-        <v>29283</v>
+        <v>30412</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5024</v>
+        <v>3632</v>
       </c>
       <c r="C3" t="n">
-        <v>7330</v>
+        <v>10472</v>
       </c>
       <c r="D3" t="n">
-        <v>15501</v>
+        <v>17702</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3341</v>
+        <v>2606</v>
       </c>
       <c r="C4" t="n">
-        <v>6037</v>
+        <v>6166</v>
       </c>
       <c r="D4" t="n">
-        <v>8383</v>
+        <v>10478</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2625</v>
+        <v>1983</v>
       </c>
       <c r="C5" t="n">
-        <v>4766</v>
+        <v>4976</v>
       </c>
       <c r="D5" t="n">
-        <v>3599</v>
+        <v>4587</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1763</v>
+        <v>1322</v>
       </c>
       <c r="C6" t="n">
-        <v>3611</v>
+        <v>4396</v>
       </c>
       <c r="D6" t="n">
-        <v>1506</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>990</v>
+        <v>717</v>
       </c>
       <c r="C7" t="n">
-        <v>2450</v>
+        <v>3231</v>
       </c>
       <c r="D7" t="n">
-        <v>751</v>
+        <v>825</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>461</v>
+        <v>327</v>
       </c>
       <c r="C8" t="n">
-        <v>1545</v>
+        <v>1975</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>177</v>
+        <v>127</v>
       </c>
       <c r="C9" t="n">
-        <v>826</v>
+        <v>992</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>388</v>
+        <v>430</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1612,10 +1612,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8598</v>
+        <v>7079</v>
       </c>
       <c r="C2" t="n">
-        <v>9918</v>
+        <v>12547</v>
       </c>
       <c r="D2" t="n">
-        <v>24170</v>
+        <v>25179</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6014</v>
+        <v>4448</v>
       </c>
       <c r="C3" t="n">
-        <v>11279</v>
+        <v>14427</v>
       </c>
       <c r="D3" t="n">
-        <v>16712</v>
+        <v>19363</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2425</v>
+        <v>1832</v>
       </c>
       <c r="C4" t="n">
-        <v>7878</v>
+        <v>8032</v>
       </c>
       <c r="D4" t="n">
-        <v>7960</v>
+        <v>10010</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1629</v>
+        <v>1221</v>
       </c>
       <c r="C5" t="n">
-        <v>3538</v>
+        <v>4308</v>
       </c>
       <c r="D5" t="n">
-        <v>2443</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>914</v>
+        <v>662</v>
       </c>
       <c r="C6" t="n">
-        <v>2401</v>
+        <v>3166</v>
       </c>
       <c r="D6" t="n">
-        <v>735</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>425</v>
+        <v>302</v>
       </c>
       <c r="C7" t="n">
-        <v>1514</v>
+        <v>1935</v>
       </c>
       <c r="D7" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="C8" t="n">
-        <v>809</v>
+        <v>972</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>380</v>
+        <v>421</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
         <v>201</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1909,10 +1909,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5342</v>
+        <v>4234</v>
       </c>
       <c r="C2" t="n">
-        <v>4611</v>
+        <v>6248</v>
       </c>
       <c r="D2" t="n">
-        <v>16774</v>
+        <v>17442</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6133</v>
+        <v>4729</v>
       </c>
       <c r="C3" t="n">
-        <v>9677</v>
+        <v>12397</v>
       </c>
       <c r="D3" t="n">
-        <v>16763</v>
+        <v>19023</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3291</v>
+        <v>2414</v>
       </c>
       <c r="C4" t="n">
-        <v>9508</v>
+        <v>10920</v>
       </c>
       <c r="D4" t="n">
-        <v>9215</v>
+        <v>11244</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1826</v>
+        <v>1351</v>
       </c>
       <c r="C5" t="n">
-        <v>5425</v>
+        <v>5890</v>
       </c>
       <c r="D5" t="n">
-        <v>3104</v>
+        <v>3793</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1083</v>
+        <v>783</v>
       </c>
       <c r="C6" t="n">
-        <v>2916</v>
+        <v>3702</v>
       </c>
       <c r="D6" t="n">
-        <v>911</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>280</v>
       </c>
       <c r="C7" t="n">
-        <v>1890</v>
+        <v>2418</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>1047</v>
+        <v>1255</v>
       </c>
       <c r="D8" t="n">
-        <v>337</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>428</v>
+        <v>458</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
         <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6421</v>
+        <v>4367</v>
       </c>
       <c r="C2" t="n">
-        <v>7962</v>
+        <v>7853</v>
       </c>
       <c r="D2" t="n">
-        <v>17323</v>
+        <v>21172</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4920</v>
+        <v>3846</v>
       </c>
       <c r="C3" t="n">
-        <v>6470</v>
+        <v>8518</v>
       </c>
       <c r="D3" t="n">
-        <v>15638</v>
+        <v>17712</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3852</v>
+        <v>2867</v>
       </c>
       <c r="C4" t="n">
-        <v>9392</v>
+        <v>11387</v>
       </c>
       <c r="D4" t="n">
-        <v>10166</v>
+        <v>11989</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2173</v>
+        <v>1584</v>
       </c>
       <c r="C5" t="n">
-        <v>7284</v>
+        <v>8093</v>
       </c>
       <c r="D5" t="n">
-        <v>3948</v>
+        <v>4822</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1287</v>
+        <v>923</v>
       </c>
       <c r="C6" t="n">
-        <v>3995</v>
+        <v>4592</v>
       </c>
       <c r="D6" t="n">
-        <v>1214</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>582</v>
+        <v>413</v>
       </c>
       <c r="C7" t="n">
-        <v>2350</v>
+        <v>2969</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>586</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>201</v>
+        <v>139</v>
       </c>
       <c r="C8" t="n">
-        <v>1395</v>
+        <v>1711</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>662</v>
+        <v>743</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2489,10 +2489,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3816</v>
+        <v>2671</v>
       </c>
       <c r="C2" t="n">
-        <v>3710</v>
+        <v>3868</v>
       </c>
       <c r="D2" t="n">
-        <v>12072</v>
+        <v>14952</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5136</v>
+        <v>3824</v>
       </c>
       <c r="C3" t="n">
-        <v>6774</v>
+        <v>8092</v>
       </c>
       <c r="D3" t="n">
-        <v>15462</v>
+        <v>17675</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4228</v>
+        <v>3125</v>
       </c>
       <c r="C4" t="n">
-        <v>9144</v>
+        <v>11389</v>
       </c>
       <c r="D4" t="n">
-        <v>10855</v>
+        <v>12732</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2272</v>
+        <v>1636</v>
       </c>
       <c r="C5" t="n">
-        <v>8861</v>
+        <v>9973</v>
       </c>
       <c r="D5" t="n">
-        <v>4175</v>
+        <v>4931</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1061</v>
+        <v>739</v>
       </c>
       <c r="C6" t="n">
-        <v>4789</v>
+        <v>5391</v>
       </c>
       <c r="D6" t="n">
-        <v>1196</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>185</v>
+        <v>128</v>
       </c>
       <c r="C7" t="n">
-        <v>2486</v>
+        <v>3081</v>
       </c>
       <c r="D7" t="n">
-        <v>566</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>1072</v>
+        <v>1214</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4841</v>
+        <v>3182</v>
       </c>
       <c r="C2" t="n">
-        <v>3584</v>
+        <v>5717</v>
       </c>
       <c r="D2" t="n">
-        <v>17154</v>
+        <v>18521</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3920</v>
+        <v>2885</v>
       </c>
       <c r="C3" t="n">
-        <v>4800</v>
+        <v>5649</v>
       </c>
       <c r="D3" t="n">
-        <v>14110</v>
+        <v>16166</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4048</v>
+        <v>2989</v>
       </c>
       <c r="C4" t="n">
-        <v>7926</v>
+        <v>9696</v>
       </c>
       <c r="D4" t="n">
-        <v>11232</v>
+        <v>13226</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2709</v>
+        <v>1951</v>
       </c>
       <c r="C5" t="n">
-        <v>8886</v>
+        <v>10459</v>
       </c>
       <c r="D5" t="n">
-        <v>5010</v>
+        <v>5829</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1366</v>
+        <v>950</v>
       </c>
       <c r="C6" t="n">
-        <v>6473</v>
+        <v>7200</v>
       </c>
       <c r="D6" t="n">
-        <v>1580</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>399</v>
+        <v>266</v>
       </c>
       <c r="C7" t="n">
-        <v>3412</v>
+        <v>4000</v>
       </c>
       <c r="D7" t="n">
-        <v>646</v>
+        <v>663</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>1615</v>
+        <v>1859</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>544</v>
+        <v>575</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
         <v>134</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>56</v>
+      </c>
+      <c r="D13" t="n">
         <v>60</v>
-      </c>
-      <c r="D13" t="n">
-        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>43</v>
+      </c>
+      <c r="D14" t="n">
         <v>46</v>
-      </c>
-      <c r="D14" t="n">
-        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3387</v>
+        <v>2111</v>
       </c>
       <c r="C2" t="n">
-        <v>2529</v>
+        <v>3488</v>
       </c>
       <c r="D2" t="n">
-        <v>12445</v>
+        <v>14806</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3693</v>
+        <v>2634</v>
       </c>
       <c r="C3" t="n">
-        <v>3934</v>
+        <v>5228</v>
       </c>
       <c r="D3" t="n">
-        <v>13843</v>
+        <v>15576</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3692</v>
+        <v>2700</v>
       </c>
       <c r="C4" t="n">
-        <v>6729</v>
+        <v>8258</v>
       </c>
       <c r="D4" t="n">
-        <v>11357</v>
+        <v>13444</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2961</v>
+        <v>2131</v>
       </c>
       <c r="C5" t="n">
-        <v>8701</v>
+        <v>10293</v>
       </c>
       <c r="D5" t="n">
-        <v>5562</v>
+        <v>6417</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1592</v>
+        <v>1082</v>
       </c>
       <c r="C6" t="n">
-        <v>7465</v>
+        <v>8415</v>
       </c>
       <c r="D6" t="n">
-        <v>1903</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>359</v>
+        <v>237</v>
       </c>
       <c r="C7" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="D7" t="n">
-        <v>715</v>
+        <v>752</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>2047</v>
+        <v>2334</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4695</v>
+        <v>2600</v>
       </c>
       <c r="C2" t="n">
-        <v>7174</v>
+        <v>7856</v>
       </c>
       <c r="D2" t="n">
-        <v>11694</v>
+        <v>13462</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3020</v>
+        <v>2077</v>
       </c>
       <c r="C3" t="n">
-        <v>3042</v>
+        <v>4105</v>
       </c>
       <c r="D3" t="n">
-        <v>12789</v>
+        <v>14517</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3208</v>
+        <v>2327</v>
       </c>
       <c r="C4" t="n">
-        <v>5370</v>
+        <v>6893</v>
       </c>
       <c r="D4" t="n">
-        <v>11369</v>
+        <v>13321</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2953</v>
+        <v>2130</v>
       </c>
       <c r="C5" t="n">
-        <v>7724</v>
+        <v>9317</v>
       </c>
       <c r="D5" t="n">
-        <v>6171</v>
+        <v>7098</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1879</v>
+        <v>1291</v>
       </c>
       <c r="C6" t="n">
-        <v>7950</v>
+        <v>9016</v>
       </c>
       <c r="D6" t="n">
-        <v>2335</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>660</v>
+        <v>428</v>
       </c>
       <c r="C7" t="n">
-        <v>5486</v>
+        <v>6144</v>
       </c>
       <c r="D7" t="n">
-        <v>847</v>
+        <v>883</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="C8" t="n">
-        <v>2840</v>
+        <v>3205</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>1085</v>
+        <v>1117</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
+        <v>83</v>
+      </c>
+      <c r="D12" t="n">
         <v>92</v>
-      </c>
-      <c r="D12" t="n">
-        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8243</v>
+        <v>5473</v>
       </c>
       <c r="C2" t="n">
-        <v>7842</v>
+        <v>11248</v>
       </c>
       <c r="D2" t="n">
-        <v>5672</v>
+        <v>14676</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3399</v>
+        <v>1921</v>
       </c>
       <c r="C2" t="n">
-        <v>4132</v>
+        <v>4713</v>
       </c>
       <c r="D2" t="n">
-        <v>8701</v>
+        <v>10015</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3987</v>
+        <v>2729</v>
       </c>
       <c r="C3" t="n">
-        <v>4235</v>
+        <v>5368</v>
       </c>
       <c r="D3" t="n">
-        <v>13696</v>
+        <v>15713</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4368</v>
+        <v>3157</v>
       </c>
       <c r="C4" t="n">
-        <v>7894</v>
+        <v>9980</v>
       </c>
       <c r="D4" t="n">
-        <v>11631</v>
+        <v>13536</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1790</v>
+        <v>1192</v>
       </c>
       <c r="C5" t="n">
-        <v>11278</v>
+        <v>13057</v>
       </c>
       <c r="D5" t="n">
-        <v>5587</v>
+        <v>6329</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>609</v>
+        <v>395</v>
       </c>
       <c r="C6" t="n">
-        <v>6856</v>
+        <v>7523</v>
       </c>
       <c r="D6" t="n">
-        <v>1866</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="C7" t="n">
-        <v>2783</v>
+        <v>3140</v>
       </c>
       <c r="D7" t="n">
-        <v>535</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>1063</v>
+        <v>1094</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
+        <v>81</v>
+      </c>
+      <c r="D11" t="n">
         <v>90</v>
-      </c>
-      <c r="D11" t="n">
-        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7566</v>
+        <v>6778</v>
       </c>
       <c r="C2" t="n">
-        <v>4749</v>
+        <v>5770</v>
       </c>
       <c r="D2" t="n">
-        <v>8653</v>
+        <v>16030</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3500</v>
+        <v>2326</v>
       </c>
       <c r="C3" t="n">
-        <v>3952</v>
+        <v>5668</v>
       </c>
       <c r="D3" t="n">
-        <v>1592</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6351</v>
+        <v>4170</v>
       </c>
       <c r="C2" t="n">
-        <v>5716</v>
+        <v>7837</v>
       </c>
       <c r="D2" t="n">
-        <v>25680</v>
+        <v>25718</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4548</v>
+        <v>3736</v>
       </c>
       <c r="C3" t="n">
-        <v>3797</v>
+        <v>4937</v>
       </c>
       <c r="D3" t="n">
-        <v>2661</v>
+        <v>5047</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1554</v>
+        <v>1045</v>
       </c>
       <c r="C4" t="n">
-        <v>2358</v>
+        <v>3365</v>
       </c>
       <c r="D4" t="n">
-        <v>1502</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5644</v>
+        <v>5557</v>
       </c>
       <c r="C2" t="n">
-        <v>5380</v>
+        <v>8413</v>
       </c>
       <c r="D2" t="n">
-        <v>24621</v>
+        <v>38555</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4465</v>
+        <v>3258</v>
       </c>
       <c r="C3" t="n">
-        <v>4192</v>
+        <v>5626</v>
       </c>
       <c r="D3" t="n">
-        <v>6152</v>
+        <v>7990</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2600</v>
+        <v>2031</v>
       </c>
       <c r="C4" t="n">
-        <v>3124</v>
+        <v>4137</v>
       </c>
       <c r="D4" t="n">
-        <v>1678</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>684</v>
+        <v>481</v>
       </c>
       <c r="C5" t="n">
-        <v>1385</v>
+        <v>1938</v>
       </c>
       <c r="D5" t="n">
-        <v>1196</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
         <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>631</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7165</v>
+        <v>5560</v>
       </c>
       <c r="C2" t="n">
-        <v>4218</v>
+        <v>7510</v>
       </c>
       <c r="D2" t="n">
-        <v>24598</v>
+        <v>30636</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4138</v>
+        <v>3543</v>
       </c>
       <c r="C3" t="n">
-        <v>4180</v>
+        <v>6132</v>
       </c>
       <c r="D3" t="n">
-        <v>8526</v>
+        <v>12073</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3006</v>
+        <v>2245</v>
       </c>
       <c r="C4" t="n">
-        <v>3633</v>
+        <v>4837</v>
       </c>
       <c r="D4" t="n">
-        <v>2443</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1350</v>
+        <v>1014</v>
       </c>
       <c r="C5" t="n">
-        <v>2244</v>
+        <v>2997</v>
       </c>
       <c r="D5" t="n">
-        <v>1231</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>357</v>
+        <v>271</v>
       </c>
       <c r="C6" t="n">
-        <v>851</v>
+        <v>1116</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
         <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8652</v>
+        <v>6209</v>
       </c>
       <c r="C2" t="n">
-        <v>9188</v>
+        <v>7964</v>
       </c>
       <c r="D2" t="n">
-        <v>24321</v>
+        <v>34091</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4070</v>
+        <v>3267</v>
       </c>
       <c r="C3" t="n">
-        <v>3440</v>
+        <v>5593</v>
       </c>
       <c r="D3" t="n">
-        <v>9754</v>
+        <v>13213</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2204</v>
+        <v>1771</v>
       </c>
       <c r="C4" t="n">
-        <v>3222</v>
+        <v>4530</v>
       </c>
       <c r="D4" t="n">
-        <v>3036</v>
+        <v>4208</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1142</v>
+        <v>848</v>
       </c>
       <c r="C5" t="n">
-        <v>2148</v>
+        <v>2848</v>
       </c>
       <c r="D5" t="n">
-        <v>1126</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>400</v>
+        <v>297</v>
       </c>
       <c r="C6" t="n">
-        <v>1046</v>
+        <v>1377</v>
       </c>
       <c r="D6" t="n">
-        <v>756</v>
+        <v>768</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>379</v>
+        <v>459</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7507</v>
+        <v>6134</v>
       </c>
       <c r="C2" t="n">
-        <v>8291</v>
+        <v>7915</v>
       </c>
       <c r="D2" t="n">
-        <v>29071</v>
+        <v>25694</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5298</v>
+        <v>3897</v>
       </c>
       <c r="C3" t="n">
-        <v>5893</v>
+        <v>5990</v>
       </c>
       <c r="D3" t="n">
-        <v>11677</v>
+        <v>15748</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2757</v>
+        <v>2174</v>
       </c>
       <c r="C4" t="n">
-        <v>3288</v>
+        <v>5068</v>
       </c>
       <c r="D4" t="n">
-        <v>4268</v>
+        <v>5895</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1485</v>
+        <v>1161</v>
       </c>
       <c r="C5" t="n">
-        <v>2742</v>
+        <v>3757</v>
       </c>
       <c r="D5" t="n">
-        <v>1476</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>719</v>
+        <v>521</v>
       </c>
       <c r="C6" t="n">
-        <v>1667</v>
+        <v>2179</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>874</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>230</v>
+        <v>174</v>
       </c>
       <c r="C7" t="n">
-        <v>757</v>
+        <v>962</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6065</v>
+        <v>5146</v>
       </c>
       <c r="C2" t="n">
-        <v>7344</v>
+        <v>5785</v>
       </c>
       <c r="D2" t="n">
-        <v>22795</v>
+        <v>29169</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5244</v>
+        <v>4115</v>
       </c>
       <c r="C3" t="n">
-        <v>6232</v>
+        <v>6081</v>
       </c>
       <c r="D3" t="n">
-        <v>13619</v>
+        <v>16151</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3433</v>
+        <v>2560</v>
       </c>
       <c r="C4" t="n">
-        <v>4695</v>
+        <v>5467</v>
       </c>
       <c r="D4" t="n">
-        <v>5560</v>
+        <v>7456</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1868</v>
+        <v>1442</v>
       </c>
       <c r="C5" t="n">
-        <v>2983</v>
+        <v>4334</v>
       </c>
       <c r="D5" t="n">
-        <v>1926</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>996</v>
+        <v>757</v>
       </c>
       <c r="C6" t="n">
-        <v>2199</v>
+        <v>2972</v>
       </c>
       <c r="D6" t="n">
-        <v>918</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>420</v>
+        <v>300</v>
       </c>
       <c r="C7" t="n">
-        <v>1238</v>
+        <v>1581</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>536</v>
+        <v>643</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
         <v>241</v>
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_39_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_39_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4913</v>
+        <v>5183</v>
       </c>
       <c r="C2" t="n">
-        <v>13494</v>
+        <v>9338</v>
       </c>
       <c r="D2" t="n">
-        <v>30228</v>
+        <v>15713</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3774</v>
+        <v>3767</v>
       </c>
       <c r="C3" t="n">
-        <v>5208</v>
+        <v>6361</v>
       </c>
       <c r="D3" t="n">
-        <v>16914</v>
+        <v>11776</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2807</v>
+        <v>3069</v>
       </c>
       <c r="C4" t="n">
-        <v>5607</v>
+        <v>5523</v>
       </c>
       <c r="D4" t="n">
-        <v>8731</v>
+        <v>6155</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1702</v>
+        <v>1900</v>
       </c>
       <c r="C5" t="n">
-        <v>4798</v>
+        <v>5884</v>
       </c>
       <c r="D5" t="n">
-        <v>3243</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>972</v>
+        <v>1001</v>
       </c>
       <c r="C6" t="n">
-        <v>3553</v>
+        <v>4444</v>
       </c>
       <c r="D6" t="n">
-        <v>1257</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>444</v>
+        <v>423</v>
       </c>
       <c r="C7" t="n">
-        <v>2234</v>
+        <v>2650</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C8" t="n">
-        <v>1059</v>
+        <v>1138</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10">
@@ -895,7 +895,7 @@
         <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
         <v>245</v>
@@ -909,10 +909,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -962,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -982,7 +982,7 @@
         <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5984</v>
+        <v>5817</v>
       </c>
       <c r="C2" t="n">
-        <v>18066</v>
+        <v>10581</v>
       </c>
       <c r="D2" t="n">
-        <v>28466</v>
+        <v>19621</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3501</v>
+        <v>3584</v>
       </c>
       <c r="C3" t="n">
-        <v>7781</v>
+        <v>6761</v>
       </c>
       <c r="D3" t="n">
-        <v>17508</v>
+        <v>11507</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2768</v>
+        <v>2904</v>
       </c>
       <c r="C4" t="n">
-        <v>5306</v>
+        <v>5794</v>
       </c>
       <c r="D4" t="n">
-        <v>9638</v>
+        <v>6772</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1899</v>
+        <v>2099</v>
       </c>
       <c r="C5" t="n">
-        <v>5009</v>
+        <v>5545</v>
       </c>
       <c r="D5" t="n">
-        <v>3987</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1156</v>
+        <v>1241</v>
       </c>
       <c r="C6" t="n">
-        <v>4057</v>
+        <v>5024</v>
       </c>
       <c r="D6" t="n">
-        <v>1514</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C7" t="n">
-        <v>2767</v>
+        <v>3378</v>
       </c>
       <c r="D7" t="n">
-        <v>742</v>
+        <v>702</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="C8" t="n">
-        <v>1531</v>
+        <v>1748</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>686</v>
+        <v>707</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" t="n">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="D10" t="n">
         <v>247</v>
@@ -1223,7 +1223,7 @@
         <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1273,10 +1273,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
         <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7758</v>
+        <v>6243</v>
       </c>
       <c r="C2" t="n">
-        <v>17823</v>
+        <v>20452</v>
       </c>
       <c r="D2" t="n">
-        <v>30412</v>
+        <v>18846</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3632</v>
+        <v>3629</v>
       </c>
       <c r="C3" t="n">
-        <v>10472</v>
+        <v>7339</v>
       </c>
       <c r="D3" t="n">
-        <v>17702</v>
+        <v>11744</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2606</v>
+        <v>2707</v>
       </c>
       <c r="C4" t="n">
-        <v>6166</v>
+        <v>6017</v>
       </c>
       <c r="D4" t="n">
-        <v>10478</v>
+        <v>7247</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1983</v>
+        <v>2146</v>
       </c>
       <c r="C5" t="n">
-        <v>4976</v>
+        <v>5476</v>
       </c>
       <c r="D5" t="n">
-        <v>4587</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1322</v>
+        <v>1427</v>
       </c>
       <c r="C6" t="n">
-        <v>4396</v>
+        <v>5185</v>
       </c>
       <c r="D6" t="n">
-        <v>1826</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>717</v>
+        <v>752</v>
       </c>
       <c r="C7" t="n">
-        <v>3231</v>
+        <v>3972</v>
       </c>
       <c r="D7" t="n">
-        <v>825</v>
+        <v>759</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="C8" t="n">
-        <v>1975</v>
+        <v>2337</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C9" t="n">
-        <v>992</v>
+        <v>1084</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D10" t="n">
         <v>250</v>
@@ -1531,10 +1531,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1584,10 +1584,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
         <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7079</v>
+        <v>5837</v>
       </c>
       <c r="C2" t="n">
-        <v>12547</v>
+        <v>14398</v>
       </c>
       <c r="D2" t="n">
-        <v>25179</v>
+        <v>15640</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4448</v>
+        <v>4563</v>
       </c>
       <c r="C3" t="n">
-        <v>14427</v>
+        <v>11608</v>
       </c>
       <c r="D3" t="n">
-        <v>19363</v>
+        <v>12936</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1832</v>
+        <v>1982</v>
       </c>
       <c r="C4" t="n">
-        <v>8032</v>
+        <v>8433</v>
       </c>
       <c r="D4" t="n">
-        <v>10010</v>
+        <v>7027</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1221</v>
+        <v>1318</v>
       </c>
       <c r="C5" t="n">
-        <v>4308</v>
+        <v>5081</v>
       </c>
       <c r="D5" t="n">
-        <v>3022</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>662</v>
+        <v>694</v>
       </c>
       <c r="C6" t="n">
-        <v>3166</v>
+        <v>3892</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>743</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="C7" t="n">
-        <v>1935</v>
+        <v>2290</v>
       </c>
       <c r="D7" t="n">
-        <v>474</v>
+        <v>468</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>972</v>
+        <v>1062</v>
       </c>
       <c r="D8" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D9" t="n">
         <v>245</v>
@@ -1828,10 +1828,10 @@
         <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -1881,10 +1881,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
         <v>80</v>
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
         <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4234</v>
+        <v>3634</v>
       </c>
       <c r="C2" t="n">
-        <v>6248</v>
+        <v>6142</v>
       </c>
       <c r="D2" t="n">
-        <v>17442</v>
+        <v>11220</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4729</v>
+        <v>4425</v>
       </c>
       <c r="C3" t="n">
-        <v>12397</v>
+        <v>11665</v>
       </c>
       <c r="D3" t="n">
-        <v>19023</v>
+        <v>12682</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2414</v>
+        <v>2566</v>
       </c>
       <c r="C4" t="n">
-        <v>10920</v>
+        <v>10013</v>
       </c>
       <c r="D4" t="n">
-        <v>11244</v>
+        <v>7799</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1351</v>
+        <v>1476</v>
       </c>
       <c r="C5" t="n">
-        <v>5890</v>
+        <v>6538</v>
       </c>
       <c r="D5" t="n">
-        <v>3793</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>783</v>
+        <v>819</v>
       </c>
       <c r="C6" t="n">
-        <v>3702</v>
+        <v>4480</v>
       </c>
       <c r="D6" t="n">
-        <v>1013</v>
+        <v>893</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C7" t="n">
-        <v>2418</v>
+        <v>2899</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>507</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>1255</v>
+        <v>1393</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" t="n">
         <v>458</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -2167,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
         <v>130</v>
@@ -2178,10 +2178,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4367</v>
+        <v>4369</v>
       </c>
       <c r="C2" t="n">
-        <v>7853</v>
+        <v>6526</v>
       </c>
       <c r="D2" t="n">
-        <v>21172</v>
+        <v>12217</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3846</v>
+        <v>3454</v>
       </c>
       <c r="C3" t="n">
-        <v>8518</v>
+        <v>8167</v>
       </c>
       <c r="D3" t="n">
-        <v>17712</v>
+        <v>11630</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2867</v>
+        <v>2885</v>
       </c>
       <c r="C4" t="n">
-        <v>11387</v>
+        <v>10581</v>
       </c>
       <c r="D4" t="n">
-        <v>11989</v>
+        <v>8358</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1584</v>
+        <v>1709</v>
       </c>
       <c r="C5" t="n">
-        <v>8093</v>
+        <v>7969</v>
       </c>
       <c r="D5" t="n">
-        <v>4822</v>
+        <v>3518</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>923</v>
+        <v>985</v>
       </c>
       <c r="C6" t="n">
-        <v>4592</v>
+        <v>5370</v>
       </c>
       <c r="D6" t="n">
-        <v>1399</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C7" t="n">
-        <v>2969</v>
+        <v>3548</v>
       </c>
       <c r="D7" t="n">
-        <v>586</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>1711</v>
+        <v>1996</v>
       </c>
       <c r="D8" t="n">
-        <v>342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>743</v>
+        <v>805</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2467,7 +2467,7 @@
         <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2489,10 +2489,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2509,7 +2509,7 @@
         <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
         <v>23</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2671</v>
+        <v>2645</v>
       </c>
       <c r="C2" t="n">
-        <v>3868</v>
+        <v>3162</v>
       </c>
       <c r="D2" t="n">
-        <v>14952</v>
+        <v>8525</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3824</v>
+        <v>3533</v>
       </c>
       <c r="C3" t="n">
-        <v>8092</v>
+        <v>7419</v>
       </c>
       <c r="D3" t="n">
-        <v>17675</v>
+        <v>11430</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3125</v>
+        <v>3158</v>
       </c>
       <c r="C4" t="n">
-        <v>11389</v>
+        <v>10635</v>
       </c>
       <c r="D4" t="n">
-        <v>12732</v>
+        <v>8855</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1636</v>
+        <v>1759</v>
       </c>
       <c r="C5" t="n">
-        <v>9973</v>
+        <v>9820</v>
       </c>
       <c r="D5" t="n">
-        <v>4931</v>
+        <v>3687</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>739</v>
+        <v>767</v>
       </c>
       <c r="C6" t="n">
-        <v>5391</v>
+        <v>6305</v>
       </c>
       <c r="D6" t="n">
-        <v>1355</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C7" t="n">
-        <v>3081</v>
+        <v>3683</v>
       </c>
       <c r="D7" t="n">
-        <v>572</v>
+        <v>558</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C8" t="n">
-        <v>1214</v>
+        <v>1356</v>
       </c>
       <c r="D8" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -2764,7 +2764,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2806,7 +2806,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
         <v>22</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3182</v>
+        <v>3669</v>
       </c>
       <c r="C2" t="n">
-        <v>5717</v>
+        <v>3053</v>
       </c>
       <c r="D2" t="n">
-        <v>18521</v>
+        <v>15522</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2885</v>
+        <v>2712</v>
       </c>
       <c r="C3" t="n">
-        <v>5649</v>
+        <v>4988</v>
       </c>
       <c r="D3" t="n">
-        <v>16166</v>
+        <v>10308</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2989</v>
+        <v>2919</v>
       </c>
       <c r="C4" t="n">
-        <v>9696</v>
+        <v>8962</v>
       </c>
       <c r="D4" t="n">
-        <v>13226</v>
+        <v>8981</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1951</v>
+        <v>2052</v>
       </c>
       <c r="C5" t="n">
-        <v>10459</v>
+        <v>10062</v>
       </c>
       <c r="D5" t="n">
-        <v>5829</v>
+        <v>4319</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>950</v>
+        <v>1012</v>
       </c>
       <c r="C6" t="n">
-        <v>7200</v>
+        <v>7728</v>
       </c>
       <c r="D6" t="n">
-        <v>1783</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="C7" t="n">
-        <v>4000</v>
+        <v>4755</v>
       </c>
       <c r="D7" t="n">
-        <v>663</v>
+        <v>620</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>1859</v>
+        <v>2180</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>575</v>
+        <v>628</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>46</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2111</v>
+        <v>2468</v>
       </c>
       <c r="C2" t="n">
-        <v>3488</v>
+        <v>2327</v>
       </c>
       <c r="D2" t="n">
-        <v>14806</v>
+        <v>11820</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2634</v>
+        <v>2632</v>
       </c>
       <c r="C3" t="n">
-        <v>5228</v>
+        <v>3923</v>
       </c>
       <c r="D3" t="n">
-        <v>15576</v>
+        <v>10347</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2700</v>
+        <v>2611</v>
       </c>
       <c r="C4" t="n">
-        <v>8258</v>
+        <v>7507</v>
       </c>
       <c r="D4" t="n">
-        <v>13444</v>
+        <v>8959</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2131</v>
+        <v>2209</v>
       </c>
       <c r="C5" t="n">
-        <v>10293</v>
+        <v>9772</v>
       </c>
       <c r="D5" t="n">
-        <v>6417</v>
+        <v>4762</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1082</v>
+        <v>1168</v>
       </c>
       <c r="C6" t="n">
-        <v>8415</v>
+        <v>8729</v>
       </c>
       <c r="D6" t="n">
-        <v>2107</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C7" t="n">
-        <v>4962</v>
+        <v>5749</v>
       </c>
       <c r="D7" t="n">
-        <v>752</v>
+        <v>685</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>2334</v>
+        <v>2761</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>611</v>
+        <v>693</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2600</v>
+        <v>2996</v>
       </c>
       <c r="C2" t="n">
-        <v>7856</v>
+        <v>5783</v>
       </c>
       <c r="D2" t="n">
-        <v>13462</v>
+        <v>13774</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2077</v>
+        <v>2171</v>
       </c>
       <c r="C3" t="n">
-        <v>4105</v>
+        <v>2966</v>
       </c>
       <c r="D3" t="n">
-        <v>14517</v>
+        <v>9866</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2327</v>
+        <v>2275</v>
       </c>
       <c r="C4" t="n">
-        <v>6893</v>
+        <v>5905</v>
       </c>
       <c r="D4" t="n">
-        <v>13321</v>
+        <v>8873</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2130</v>
+        <v>2161</v>
       </c>
       <c r="C5" t="n">
-        <v>9317</v>
+        <v>8698</v>
       </c>
       <c r="D5" t="n">
-        <v>7098</v>
+        <v>5095</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1291</v>
+        <v>1379</v>
       </c>
       <c r="C6" t="n">
-        <v>9016</v>
+        <v>9039</v>
       </c>
       <c r="D6" t="n">
-        <v>2576</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>428</v>
+        <v>461</v>
       </c>
       <c r="C7" t="n">
-        <v>6144</v>
+        <v>6798</v>
       </c>
       <c r="D7" t="n">
-        <v>883</v>
+        <v>797</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C8" t="n">
-        <v>3205</v>
+        <v>3782</v>
       </c>
       <c r="D8" t="n">
-        <v>424</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>1117</v>
+        <v>1320</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>329</v>
+        <v>355</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
         <v>92</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
         <v>62</v>
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5473</v>
+        <v>4408</v>
       </c>
       <c r="C2" t="n">
-        <v>11248</v>
+        <v>9790</v>
       </c>
       <c r="D2" t="n">
-        <v>14676</v>
+        <v>7810</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1921</v>
+        <v>2190</v>
       </c>
       <c r="C2" t="n">
-        <v>4713</v>
+        <v>3423</v>
       </c>
       <c r="D2" t="n">
-        <v>10015</v>
+        <v>10247</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2729</v>
+        <v>2821</v>
       </c>
       <c r="C3" t="n">
-        <v>5368</v>
+        <v>3879</v>
       </c>
       <c r="D3" t="n">
-        <v>15713</v>
+        <v>10924</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3157</v>
+        <v>3159</v>
       </c>
       <c r="C4" t="n">
-        <v>9980</v>
+        <v>8762</v>
       </c>
       <c r="D4" t="n">
-        <v>13536</v>
+        <v>9059</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1192</v>
+        <v>1294</v>
       </c>
       <c r="C5" t="n">
-        <v>13057</v>
+        <v>12691</v>
       </c>
       <c r="D5" t="n">
-        <v>6329</v>
+        <v>4699</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="C6" t="n">
-        <v>7523</v>
+        <v>8256</v>
       </c>
       <c r="D6" t="n">
-        <v>1998</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C7" t="n">
-        <v>3140</v>
+        <v>3706</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>1094</v>
+        <v>1293</v>
       </c>
       <c r="D8" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="D9" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
         <v>90</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
         <v>60</v>
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6778</v>
+        <v>6500</v>
       </c>
       <c r="C2" t="n">
-        <v>5770</v>
+        <v>8701</v>
       </c>
       <c r="D2" t="n">
-        <v>16030</v>
+        <v>16940</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2326</v>
+        <v>1874</v>
       </c>
       <c r="C3" t="n">
-        <v>5668</v>
+        <v>4934</v>
       </c>
       <c r="D3" t="n">
-        <v>3104</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="4">
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4170</v>
+        <v>5011</v>
       </c>
       <c r="C2" t="n">
-        <v>7837</v>
+        <v>12297</v>
       </c>
       <c r="D2" t="n">
-        <v>25718</v>
+        <v>18014</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3736</v>
+        <v>3434</v>
       </c>
       <c r="C3" t="n">
-        <v>4937</v>
+        <v>6093</v>
       </c>
       <c r="D3" t="n">
-        <v>5047</v>
+        <v>4325</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1045</v>
+        <v>848</v>
       </c>
       <c r="C4" t="n">
-        <v>3365</v>
+        <v>2935</v>
       </c>
       <c r="D4" t="n">
-        <v>1806</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5557</v>
+        <v>5775</v>
       </c>
       <c r="C2" t="n">
-        <v>8413</v>
+        <v>9265</v>
       </c>
       <c r="D2" t="n">
-        <v>38555</v>
+        <v>18703</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3258</v>
+        <v>3456</v>
       </c>
       <c r="C3" t="n">
-        <v>5626</v>
+        <v>8260</v>
       </c>
       <c r="D3" t="n">
-        <v>7990</v>
+        <v>6203</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2031</v>
+        <v>1816</v>
       </c>
       <c r="C4" t="n">
-        <v>4137</v>
+        <v>4604</v>
       </c>
       <c r="D4" t="n">
-        <v>2373</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>481</v>
+        <v>401</v>
       </c>
       <c r="C5" t="n">
-        <v>1938</v>
+        <v>1700</v>
       </c>
       <c r="D5" t="n">
-        <v>1260</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>903</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5560</v>
+        <v>6937</v>
       </c>
       <c r="C2" t="n">
-        <v>7510</v>
+        <v>9627</v>
       </c>
       <c r="D2" t="n">
-        <v>30636</v>
+        <v>22985</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3543</v>
+        <v>3715</v>
       </c>
       <c r="C3" t="n">
-        <v>6132</v>
+        <v>7644</v>
       </c>
       <c r="D3" t="n">
-        <v>12073</v>
+        <v>7666</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2245</v>
+        <v>2205</v>
       </c>
       <c r="C4" t="n">
-        <v>4837</v>
+        <v>6394</v>
       </c>
       <c r="D4" t="n">
-        <v>3325</v>
+        <v>2748</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1014</v>
+        <v>907</v>
       </c>
       <c r="C5" t="n">
-        <v>2997</v>
+        <v>3170</v>
       </c>
       <c r="D5" t="n">
-        <v>1414</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>271</v>
+        <v>238</v>
       </c>
       <c r="C6" t="n">
-        <v>1116</v>
+        <v>997</v>
       </c>
       <c r="D6" t="n">
         <v>944</v>
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
         <v>342</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6209</v>
+        <v>6987</v>
       </c>
       <c r="C2" t="n">
-        <v>7964</v>
+        <v>8604</v>
       </c>
       <c r="D2" t="n">
-        <v>34091</v>
+        <v>24725</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3267</v>
+        <v>3799</v>
       </c>
       <c r="C3" t="n">
-        <v>5593</v>
+        <v>7081</v>
       </c>
       <c r="D3" t="n">
-        <v>13213</v>
+        <v>8894</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1771</v>
+        <v>1810</v>
       </c>
       <c r="C4" t="n">
-        <v>4530</v>
+        <v>5784</v>
       </c>
       <c r="D4" t="n">
-        <v>4208</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>848</v>
+        <v>804</v>
       </c>
       <c r="C5" t="n">
-        <v>2848</v>
+        <v>3491</v>
       </c>
       <c r="D5" t="n">
-        <v>1377</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>297</v>
+        <v>264</v>
       </c>
       <c r="C6" t="n">
-        <v>1377</v>
+        <v>1394</v>
       </c>
       <c r="D6" t="n">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>459</v>
+        <v>419</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
         <v>233</v>
@@ -5896,10 +5896,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
         <v>147</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6134</v>
+        <v>6042</v>
       </c>
       <c r="C2" t="n">
-        <v>7915</v>
+        <v>4574</v>
       </c>
       <c r="D2" t="n">
-        <v>25694</v>
+        <v>19762</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3897</v>
+        <v>4460</v>
       </c>
       <c r="C3" t="n">
-        <v>5990</v>
+        <v>6850</v>
       </c>
       <c r="D3" t="n">
-        <v>15748</v>
+        <v>10899</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2174</v>
+        <v>2454</v>
       </c>
       <c r="C4" t="n">
-        <v>5068</v>
+        <v>6435</v>
       </c>
       <c r="D4" t="n">
-        <v>5895</v>
+        <v>4178</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="C5" t="n">
-        <v>3757</v>
+        <v>4739</v>
       </c>
       <c r="D5" t="n">
-        <v>1865</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>521</v>
+        <v>485</v>
       </c>
       <c r="C6" t="n">
-        <v>2179</v>
+        <v>2544</v>
       </c>
       <c r="D6" t="n">
-        <v>874</v>
+        <v>842</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="C7" t="n">
-        <v>962</v>
+        <v>949</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6221,7 +6221,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
         <v>80</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>63</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6308,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5146</v>
+        <v>4880</v>
       </c>
       <c r="C2" t="n">
-        <v>5785</v>
+        <v>9851</v>
       </c>
       <c r="D2" t="n">
-        <v>29169</v>
+        <v>19038</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4115</v>
+        <v>4296</v>
       </c>
       <c r="C3" t="n">
-        <v>6081</v>
+        <v>4913</v>
       </c>
       <c r="D3" t="n">
-        <v>16151</v>
+        <v>11478</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2560</v>
+        <v>2952</v>
       </c>
       <c r="C4" t="n">
-        <v>5467</v>
+        <v>6528</v>
       </c>
       <c r="D4" t="n">
-        <v>7456</v>
+        <v>5236</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1442</v>
+        <v>1549</v>
       </c>
       <c r="C5" t="n">
-        <v>4334</v>
+        <v>5490</v>
       </c>
       <c r="D5" t="n">
-        <v>2543</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>757</v>
+        <v>736</v>
       </c>
       <c r="C6" t="n">
-        <v>2972</v>
+        <v>3653</v>
       </c>
       <c r="D6" t="n">
-        <v>1024</v>
+        <v>941</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="C7" t="n">
-        <v>1581</v>
+        <v>1761</v>
       </c>
       <c r="D7" t="n">
-        <v>610</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>643</v>
+        <v>628</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6546,7 +6546,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>69</v>
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6619,7 +6619,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>

--- a/output/yearly_population_iteration_39_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_39_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5183</v>
+        <v>1038</v>
       </c>
       <c r="C2" t="n">
-        <v>9338</v>
+        <v>2817</v>
       </c>
       <c r="D2" t="n">
-        <v>15713</v>
+        <v>20695</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3767</v>
+        <v>1697</v>
       </c>
       <c r="C3" t="n">
-        <v>6361</v>
+        <v>6746</v>
       </c>
       <c r="D3" t="n">
-        <v>11776</v>
+        <v>17162</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3069</v>
+        <v>1165</v>
       </c>
       <c r="C4" t="n">
-        <v>5523</v>
+        <v>8025</v>
       </c>
       <c r="D4" t="n">
-        <v>6155</v>
+        <v>7261</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1900</v>
+        <v>631</v>
       </c>
       <c r="C5" t="n">
-        <v>5884</v>
+        <v>3682</v>
       </c>
       <c r="D5" t="n">
-        <v>2423</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1001</v>
+        <v>277</v>
       </c>
       <c r="C6" t="n">
-        <v>4444</v>
+        <v>1351</v>
       </c>
       <c r="D6" t="n">
-        <v>1095</v>
+        <v>760</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>423</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>2650</v>
+        <v>586</v>
       </c>
       <c r="D7" t="n">
-        <v>643</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>152</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>1138</v>
+        <v>344</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>419</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>303</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5817</v>
+        <v>917</v>
       </c>
       <c r="C2" t="n">
-        <v>10581</v>
+        <v>8582</v>
       </c>
       <c r="D2" t="n">
-        <v>19621</v>
+        <v>19076</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3584</v>
+        <v>1164</v>
       </c>
       <c r="C3" t="n">
-        <v>6761</v>
+        <v>4091</v>
       </c>
       <c r="D3" t="n">
-        <v>11507</v>
+        <v>16656</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2904</v>
+        <v>1235</v>
       </c>
       <c r="C4" t="n">
-        <v>5794</v>
+        <v>7158</v>
       </c>
       <c r="D4" t="n">
-        <v>6772</v>
+        <v>8846</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2099</v>
+        <v>786</v>
       </c>
       <c r="C5" t="n">
-        <v>5545</v>
+        <v>5933</v>
       </c>
       <c r="D5" t="n">
-        <v>2922</v>
+        <v>3082</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1241</v>
+        <v>394</v>
       </c>
       <c r="C6" t="n">
-        <v>5024</v>
+        <v>2513</v>
       </c>
       <c r="D6" t="n">
-        <v>1261</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>587</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>3378</v>
+        <v>958</v>
       </c>
       <c r="D7" t="n">
-        <v>702</v>
+        <v>530</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>1748</v>
+        <v>456</v>
       </c>
       <c r="D8" t="n">
-        <v>451</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>707</v>
+        <v>316</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>294</v>
+        <v>245</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6243</v>
+        <v>479</v>
       </c>
       <c r="C2" t="n">
-        <v>20452</v>
+        <v>3539</v>
       </c>
       <c r="D2" t="n">
-        <v>18846</v>
+        <v>12848</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3629</v>
+        <v>1060</v>
       </c>
       <c r="C3" t="n">
-        <v>7339</v>
+        <v>5681</v>
       </c>
       <c r="D3" t="n">
-        <v>11744</v>
+        <v>16512</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2707</v>
+        <v>1349</v>
       </c>
       <c r="C4" t="n">
-        <v>6017</v>
+        <v>6557</v>
       </c>
       <c r="D4" t="n">
-        <v>7247</v>
+        <v>9986</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2146</v>
+        <v>802</v>
       </c>
       <c r="C5" t="n">
-        <v>5476</v>
+        <v>6936</v>
       </c>
       <c r="D5" t="n">
-        <v>3322</v>
+        <v>3471</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1427</v>
+        <v>326</v>
       </c>
       <c r="C6" t="n">
-        <v>5185</v>
+        <v>3399</v>
       </c>
       <c r="D6" t="n">
-        <v>1467</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>752</v>
+        <v>73</v>
       </c>
       <c r="C7" t="n">
-        <v>3972</v>
+        <v>971</v>
       </c>
       <c r="D7" t="n">
-        <v>759</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>316</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>2337</v>
+        <v>470</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>119</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>1084</v>
+        <v>240</v>
       </c>
       <c r="D9" t="n">
-        <v>326</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>432</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>218</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5837</v>
+        <v>946</v>
       </c>
       <c r="C2" t="n">
-        <v>14398</v>
+        <v>3999</v>
       </c>
       <c r="D2" t="n">
-        <v>15640</v>
+        <v>17084</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4563</v>
+        <v>682</v>
       </c>
       <c r="C3" t="n">
-        <v>11608</v>
+        <v>4039</v>
       </c>
       <c r="D3" t="n">
-        <v>12936</v>
+        <v>14951</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1982</v>
+        <v>1086</v>
       </c>
       <c r="C4" t="n">
-        <v>8433</v>
+        <v>6021</v>
       </c>
       <c r="D4" t="n">
-        <v>7027</v>
+        <v>10810</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1318</v>
+        <v>934</v>
       </c>
       <c r="C5" t="n">
-        <v>5081</v>
+        <v>6669</v>
       </c>
       <c r="D5" t="n">
-        <v>2330</v>
+        <v>4428</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>694</v>
+        <v>474</v>
       </c>
       <c r="C6" t="n">
-        <v>3892</v>
+        <v>5061</v>
       </c>
       <c r="D6" t="n">
-        <v>743</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>291</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>2290</v>
+        <v>2084</v>
       </c>
       <c r="D7" t="n">
-        <v>468</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>1062</v>
+        <v>689</v>
       </c>
       <c r="D8" t="n">
-        <v>319</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>423</v>
+        <v>330</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3634</v>
+        <v>503</v>
       </c>
       <c r="C2" t="n">
-        <v>6142</v>
+        <v>2069</v>
       </c>
       <c r="D2" t="n">
-        <v>11220</v>
+        <v>13042</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4425</v>
+        <v>680</v>
       </c>
       <c r="C3" t="n">
-        <v>11665</v>
+        <v>3647</v>
       </c>
       <c r="D3" t="n">
-        <v>12682</v>
+        <v>14379</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2566</v>
+        <v>878</v>
       </c>
       <c r="C4" t="n">
-        <v>10013</v>
+        <v>5098</v>
       </c>
       <c r="D4" t="n">
-        <v>7799</v>
+        <v>11324</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1476</v>
+        <v>966</v>
       </c>
       <c r="C5" t="n">
-        <v>6538</v>
+        <v>6576</v>
       </c>
       <c r="D5" t="n">
-        <v>2844</v>
+        <v>5132</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>819</v>
+        <v>568</v>
       </c>
       <c r="C6" t="n">
-        <v>4480</v>
+        <v>5840</v>
       </c>
       <c r="D6" t="n">
-        <v>893</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>271</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>2899</v>
+        <v>3101</v>
       </c>
       <c r="D7" t="n">
-        <v>507</v>
+        <v>684</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1393</v>
+        <v>1043</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>458</v>
+        <v>421</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4369</v>
+        <v>708</v>
       </c>
       <c r="C2" t="n">
-        <v>6526</v>
+        <v>7458</v>
       </c>
       <c r="D2" t="n">
-        <v>12217</v>
+        <v>11929</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3454</v>
+        <v>510</v>
       </c>
       <c r="C3" t="n">
-        <v>8167</v>
+        <v>2594</v>
       </c>
       <c r="D3" t="n">
-        <v>11630</v>
+        <v>13230</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2885</v>
+        <v>701</v>
       </c>
       <c r="C4" t="n">
-        <v>10581</v>
+        <v>4295</v>
       </c>
       <c r="D4" t="n">
-        <v>8358</v>
+        <v>11478</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1709</v>
+        <v>855</v>
       </c>
       <c r="C5" t="n">
-        <v>7969</v>
+        <v>5758</v>
       </c>
       <c r="D5" t="n">
-        <v>3518</v>
+        <v>5927</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>985</v>
+        <v>672</v>
       </c>
       <c r="C6" t="n">
-        <v>5370</v>
+        <v>6166</v>
       </c>
       <c r="D6" t="n">
-        <v>1162</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>417</v>
+        <v>278</v>
       </c>
       <c r="C7" t="n">
-        <v>3548</v>
+        <v>4253</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>820</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>1996</v>
+        <v>1879</v>
       </c>
       <c r="D8" t="n">
-        <v>350</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>805</v>
+        <v>656</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>386</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2645</v>
+        <v>475</v>
       </c>
       <c r="C2" t="n">
-        <v>3162</v>
+        <v>3878</v>
       </c>
       <c r="D2" t="n">
-        <v>8525</v>
+        <v>8589</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3533</v>
+        <v>722</v>
       </c>
       <c r="C3" t="n">
-        <v>7419</v>
+        <v>4155</v>
       </c>
       <c r="D3" t="n">
-        <v>11430</v>
+        <v>14206</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3158</v>
+        <v>1134</v>
       </c>
       <c r="C4" t="n">
-        <v>10635</v>
+        <v>6039</v>
       </c>
       <c r="D4" t="n">
-        <v>8855</v>
+        <v>11776</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1759</v>
+        <v>676</v>
       </c>
       <c r="C5" t="n">
-        <v>9820</v>
+        <v>8567</v>
       </c>
       <c r="D5" t="n">
-        <v>3687</v>
+        <v>5414</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>767</v>
+        <v>256</v>
       </c>
       <c r="C6" t="n">
-        <v>6305</v>
+        <v>5678</v>
       </c>
       <c r="D6" t="n">
-        <v>1137</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>3683</v>
+        <v>1841</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>1356</v>
+        <v>642</v>
       </c>
       <c r="D8" t="n">
-        <v>371</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>162</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3669</v>
+        <v>264</v>
       </c>
       <c r="C2" t="n">
-        <v>3053</v>
+        <v>2329</v>
       </c>
       <c r="D2" t="n">
-        <v>15522</v>
+        <v>6332</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2712</v>
+        <v>521</v>
       </c>
       <c r="C3" t="n">
-        <v>4988</v>
+        <v>3539</v>
       </c>
       <c r="D3" t="n">
-        <v>10308</v>
+        <v>12378</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2919</v>
+        <v>784</v>
       </c>
       <c r="C4" t="n">
-        <v>8962</v>
+        <v>4815</v>
       </c>
       <c r="D4" t="n">
-        <v>8981</v>
+        <v>11351</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2052</v>
+        <v>624</v>
       </c>
       <c r="C5" t="n">
-        <v>10062</v>
+        <v>6481</v>
       </c>
       <c r="D5" t="n">
-        <v>4319</v>
+        <v>5703</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1012</v>
+        <v>248</v>
       </c>
       <c r="C6" t="n">
-        <v>7728</v>
+        <v>5732</v>
       </c>
       <c r="D6" t="n">
-        <v>1476</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>274</v>
+        <v>61</v>
       </c>
       <c r="C7" t="n">
-        <v>4755</v>
+        <v>2495</v>
       </c>
       <c r="D7" t="n">
-        <v>620</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>2180</v>
+        <v>727</v>
       </c>
       <c r="D8" t="n">
-        <v>391</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>628</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>128</v>
       </c>
       <c r="D10" t="n">
-        <v>171</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2468</v>
+        <v>311</v>
       </c>
       <c r="C2" t="n">
-        <v>2327</v>
+        <v>3096</v>
       </c>
       <c r="D2" t="n">
-        <v>11820</v>
+        <v>9594</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2632</v>
+        <v>332</v>
       </c>
       <c r="C3" t="n">
-        <v>3923</v>
+        <v>2507</v>
       </c>
       <c r="D3" t="n">
-        <v>10347</v>
+        <v>10519</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2611</v>
+        <v>580</v>
       </c>
       <c r="C4" t="n">
-        <v>7507</v>
+        <v>4004</v>
       </c>
       <c r="D4" t="n">
-        <v>8959</v>
+        <v>11203</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2209</v>
+        <v>634</v>
       </c>
       <c r="C5" t="n">
-        <v>9772</v>
+        <v>5512</v>
       </c>
       <c r="D5" t="n">
-        <v>4762</v>
+        <v>6559</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1168</v>
+        <v>381</v>
       </c>
       <c r="C6" t="n">
-        <v>8729</v>
+        <v>6050</v>
       </c>
       <c r="D6" t="n">
-        <v>1705</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>242</v>
+        <v>125</v>
       </c>
       <c r="C7" t="n">
-        <v>5749</v>
+        <v>4136</v>
       </c>
       <c r="D7" t="n">
-        <v>685</v>
+        <v>820</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>2761</v>
+        <v>1565</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>693</v>
+        <v>471</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2996</v>
+        <v>266</v>
       </c>
       <c r="C2" t="n">
-        <v>5783</v>
+        <v>5570</v>
       </c>
       <c r="D2" t="n">
-        <v>13774</v>
+        <v>14902</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2171</v>
+        <v>270</v>
       </c>
       <c r="C3" t="n">
-        <v>2966</v>
+        <v>2468</v>
       </c>
       <c r="D3" t="n">
-        <v>9866</v>
+        <v>9662</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2275</v>
+        <v>406</v>
       </c>
       <c r="C4" t="n">
-        <v>5905</v>
+        <v>3120</v>
       </c>
       <c r="D4" t="n">
-        <v>8873</v>
+        <v>10744</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2161</v>
+        <v>558</v>
       </c>
       <c r="C5" t="n">
-        <v>8698</v>
+        <v>4644</v>
       </c>
       <c r="D5" t="n">
-        <v>5095</v>
+        <v>7054</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1379</v>
+        <v>454</v>
       </c>
       <c r="C6" t="n">
-        <v>9039</v>
+        <v>5728</v>
       </c>
       <c r="D6" t="n">
-        <v>2064</v>
+        <v>3178</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>461</v>
+        <v>210</v>
       </c>
       <c r="C7" t="n">
-        <v>6798</v>
+        <v>5034</v>
       </c>
       <c r="D7" t="n">
-        <v>797</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>3782</v>
+        <v>2723</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>1320</v>
+        <v>942</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>355</v>
+        <v>303</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4408</v>
+        <v>4685</v>
       </c>
       <c r="C2" t="n">
-        <v>9790</v>
+        <v>7440</v>
       </c>
       <c r="D2" t="n">
-        <v>7810</v>
+        <v>17389</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2190</v>
+        <v>448</v>
       </c>
       <c r="C2" t="n">
-        <v>3423</v>
+        <v>11350</v>
       </c>
       <c r="D2" t="n">
-        <v>10247</v>
+        <v>13274</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2821</v>
+        <v>225</v>
       </c>
       <c r="C3" t="n">
-        <v>3879</v>
+        <v>3391</v>
       </c>
       <c r="D3" t="n">
-        <v>10924</v>
+        <v>9818</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3159</v>
+        <v>303</v>
       </c>
       <c r="C4" t="n">
-        <v>8762</v>
+        <v>2748</v>
       </c>
       <c r="D4" t="n">
-        <v>9059</v>
+        <v>10148</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1294</v>
+        <v>459</v>
       </c>
       <c r="C5" t="n">
-        <v>12691</v>
+        <v>3859</v>
       </c>
       <c r="D5" t="n">
-        <v>4699</v>
+        <v>7406</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>425</v>
+        <v>459</v>
       </c>
       <c r="C6" t="n">
-        <v>8256</v>
+        <v>5149</v>
       </c>
       <c r="D6" t="n">
-        <v>1678</v>
+        <v>3663</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>80</v>
+        <v>277</v>
       </c>
       <c r="C7" t="n">
-        <v>3706</v>
+        <v>5331</v>
       </c>
       <c r="D7" t="n">
-        <v>516</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>1293</v>
+        <v>3673</v>
       </c>
       <c r="D8" t="n">
-        <v>288</v>
+        <v>506</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>347</v>
+        <v>1630</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>547</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6500</v>
+        <v>3734</v>
       </c>
       <c r="C2" t="n">
-        <v>8701</v>
+        <v>4776</v>
       </c>
       <c r="D2" t="n">
-        <v>16940</v>
+        <v>24923</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1874</v>
+        <v>1511</v>
       </c>
       <c r="C3" t="n">
-        <v>4934</v>
+        <v>2938</v>
       </c>
       <c r="D3" t="n">
-        <v>1951</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5011</v>
+        <v>2808</v>
       </c>
       <c r="C2" t="n">
-        <v>12297</v>
+        <v>4362</v>
       </c>
       <c r="D2" t="n">
-        <v>18014</v>
+        <v>23876</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3434</v>
+        <v>2205</v>
       </c>
       <c r="C3" t="n">
-        <v>6093</v>
+        <v>3470</v>
       </c>
       <c r="D3" t="n">
-        <v>4325</v>
+        <v>6617</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>848</v>
+        <v>724</v>
       </c>
       <c r="C4" t="n">
-        <v>2935</v>
+        <v>1880</v>
       </c>
       <c r="D4" t="n">
-        <v>1574</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>344</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5775</v>
+        <v>1744</v>
       </c>
       <c r="C2" t="n">
-        <v>9265</v>
+        <v>4251</v>
       </c>
       <c r="D2" t="n">
-        <v>18703</v>
+        <v>29529</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3456</v>
+        <v>2069</v>
       </c>
       <c r="C3" t="n">
-        <v>8260</v>
+        <v>3429</v>
       </c>
       <c r="D3" t="n">
-        <v>6203</v>
+        <v>9029</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1816</v>
+        <v>1285</v>
       </c>
       <c r="C4" t="n">
-        <v>4604</v>
+        <v>2787</v>
       </c>
       <c r="D4" t="n">
-        <v>2054</v>
+        <v>2659</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>401</v>
+        <v>355</v>
       </c>
       <c r="C5" t="n">
-        <v>1700</v>
+        <v>1166</v>
       </c>
       <c r="D5" t="n">
-        <v>1218</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>333</v>
       </c>
       <c r="D7" t="n">
-        <v>629</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6937</v>
+        <v>1897</v>
       </c>
       <c r="C2" t="n">
-        <v>9627</v>
+        <v>10520</v>
       </c>
       <c r="D2" t="n">
-        <v>22985</v>
+        <v>24741</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3715</v>
+        <v>1578</v>
       </c>
       <c r="C3" t="n">
-        <v>7644</v>
+        <v>3357</v>
       </c>
       <c r="D3" t="n">
-        <v>7666</v>
+        <v>11658</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2205</v>
+        <v>1450</v>
       </c>
       <c r="C4" t="n">
-        <v>6394</v>
+        <v>3098</v>
       </c>
       <c r="D4" t="n">
-        <v>2748</v>
+        <v>3775</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>907</v>
+        <v>702</v>
       </c>
       <c r="C5" t="n">
-        <v>3170</v>
+        <v>2044</v>
       </c>
       <c r="D5" t="n">
-        <v>1313</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>238</v>
+        <v>207</v>
       </c>
       <c r="C6" t="n">
-        <v>997</v>
+        <v>745</v>
       </c>
       <c r="D6" t="n">
-        <v>944</v>
+        <v>845</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>308</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>249</v>
       </c>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6987</v>
+        <v>1602</v>
       </c>
       <c r="C2" t="n">
-        <v>8604</v>
+        <v>10339</v>
       </c>
       <c r="D2" t="n">
-        <v>24725</v>
+        <v>26687</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3799</v>
+        <v>1425</v>
       </c>
       <c r="C3" t="n">
-        <v>7081</v>
+        <v>6182</v>
       </c>
       <c r="D3" t="n">
-        <v>8894</v>
+        <v>12825</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1810</v>
+        <v>1299</v>
       </c>
       <c r="C4" t="n">
-        <v>5784</v>
+        <v>3175</v>
       </c>
       <c r="D4" t="n">
-        <v>3106</v>
+        <v>5061</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>804</v>
+        <v>931</v>
       </c>
       <c r="C5" t="n">
-        <v>3491</v>
+        <v>2557</v>
       </c>
       <c r="D5" t="n">
-        <v>1221</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>264</v>
+        <v>394</v>
       </c>
       <c r="C6" t="n">
-        <v>1394</v>
+        <v>1397</v>
       </c>
       <c r="D6" t="n">
-        <v>766</v>
+        <v>928</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="C7" t="n">
-        <v>419</v>
+        <v>516</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>276</v>
       </c>
       <c r="D9" t="n">
-        <v>274</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6042</v>
+        <v>2280</v>
       </c>
       <c r="C2" t="n">
-        <v>4574</v>
+        <v>8351</v>
       </c>
       <c r="D2" t="n">
-        <v>19762</v>
+        <v>38654</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4460</v>
+        <v>1244</v>
       </c>
       <c r="C3" t="n">
-        <v>6850</v>
+        <v>7196</v>
       </c>
       <c r="D3" t="n">
-        <v>10899</v>
+        <v>13938</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2454</v>
+        <v>1177</v>
       </c>
       <c r="C4" t="n">
-        <v>6435</v>
+        <v>4667</v>
       </c>
       <c r="D4" t="n">
-        <v>4178</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1157</v>
+        <v>974</v>
       </c>
       <c r="C5" t="n">
-        <v>4739</v>
+        <v>2812</v>
       </c>
       <c r="D5" t="n">
-        <v>1534</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>485</v>
+        <v>579</v>
       </c>
       <c r="C6" t="n">
-        <v>2544</v>
+        <v>1939</v>
       </c>
       <c r="D6" t="n">
-        <v>842</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>157</v>
+        <v>224</v>
       </c>
       <c r="C7" t="n">
-        <v>949</v>
+        <v>925</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>649</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>328</v>
+        <v>399</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>242</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4880</v>
+        <v>2014</v>
       </c>
       <c r="C2" t="n">
-        <v>9851</v>
+        <v>5077</v>
       </c>
       <c r="D2" t="n">
-        <v>19038</v>
+        <v>30263</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4296</v>
+        <v>1871</v>
       </c>
       <c r="C3" t="n">
-        <v>4913</v>
+        <v>10034</v>
       </c>
       <c r="D3" t="n">
-        <v>11478</v>
+        <v>15766</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2952</v>
+        <v>899</v>
       </c>
       <c r="C4" t="n">
-        <v>6528</v>
+        <v>5656</v>
       </c>
       <c r="D4" t="n">
-        <v>5236</v>
+        <v>5746</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1549</v>
+        <v>534</v>
       </c>
       <c r="C5" t="n">
-        <v>5490</v>
+        <v>1900</v>
       </c>
       <c r="D5" t="n">
-        <v>1969</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>736</v>
+        <v>206</v>
       </c>
       <c r="C6" t="n">
-        <v>3653</v>
+        <v>906</v>
       </c>
       <c r="D6" t="n">
-        <v>941</v>
+        <v>636</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>276</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>1761</v>
+        <v>391</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>628</v>
+        <v>280</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
